--- a/resources/office-templates/02-line-three-waves.xlsx
+++ b/resources/office-templates/02-line-three-waves.xlsx
@@ -185,7 +185,7 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
               <a:solidFill>
-                <a:srgbClr val="5D7F58"/>
+                <a:srgbClr val="A8821F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -255,7 +255,7 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
               <a:solidFill>
-                <a:srgbClr val="A8821F"/>
+                <a:srgbClr val="5D7F58"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1140,14 +1140,14 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Pattern B:類別配色（綠 / 藍 / 黃,LINE_COLORS 加深版）</t>
+          <t>Pattern B:類別配色,最新波次用主色作為焦點</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>折線使用加深版色彩以滿足 WCAG AA(細線對比 ≥ 3:1)。3 條序列順序代表優先級。</t>
+          <t>最新一波(2024)用主色 #5D7F58 作為焦點,歷史波次依時間遞遠遞弱(2023 藍 / 2022 黃)。LINE_COLORS 加深版確保 WCAG AA(細線對比 ≥ 3:1)。</t>
         </is>
       </c>
     </row>
